--- a/StoryTracker.xlsx
+++ b/StoryTracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ABHIJEET\JAVA_Projects\LinkedIn_Clone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff7f39e3a6d00a1d/Documents/GitHub/JobSearchApp/JobSearchApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A82C00-0598-49A4-BB74-AA655BF3D5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{F3A82C00-0598-49A4-BB74-AA655BF3D5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14E36BA0-099A-4E89-A564-FA6B0BC0068C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{F6C8B1BE-27CB-4AF5-9F37-AF67A5389A82}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="193">
   <si>
     <t>Sr No</t>
   </si>
@@ -823,6 +823,15 @@
   <si>
     <t>Initial Push</t>
   </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Add User Details Added, Other Crud operation is in progress</t>
+  </si>
+  <si>
+    <t>2A-AddUserDetails Added</t>
+  </si>
 </sst>
 </file>
 
@@ -909,29 +918,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -959,9 +953,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -993,6 +984,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1001,6 +995,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1365,1437 +1374,1444 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9B6291-A0EC-4E0E-BD5E-B6EBD7F413DA}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46" style="35" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="31" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="31" customWidth="1"/>
-    <col min="8" max="9" width="18.85546875" style="31" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46" style="29" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="25" customWidth="1"/>
+    <col min="8" max="9" width="18.85546875" style="25" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-    </row>
-    <row r="2" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23">
+      <c r="A3" s="18">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="20">
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="32">
+      <c r="G3" s="18"/>
+      <c r="H3" s="26">
         <v>46046</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="26">
         <v>46046</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23">
+      <c r="A4" s="18">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="20">
         <v>1</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="32">
+      <c r="G4" s="18"/>
+      <c r="H4" s="26">
         <v>46046</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="26">
         <v>46046</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23">
+      <c r="A5" s="18">
         <v>3</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="20">
         <v>1</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="32">
+      <c r="G5" s="18"/>
+      <c r="H5" s="26">
         <v>46047</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="26">
         <v>46047</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23">
+      <c r="A6" s="18">
         <v>4</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="21">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="32">
+      <c r="G6" s="18"/>
+      <c r="H6" s="26">
         <v>46047</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="26">
         <v>46047</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="18">
         <v>5</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="20">
         <v>1</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="32">
+      <c r="G7" s="18"/>
+      <c r="H7" s="26">
         <v>46047</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="26">
         <v>46047</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23">
+      <c r="A8" s="18">
         <v>6</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="22">
         <v>0.7</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="32">
+      <c r="G8" s="18"/>
+      <c r="H8" s="26">
         <v>46047</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="26">
         <v>46047</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+      <c r="A10" s="18">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="21">
         <v>0</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23">
+      <c r="A11" s="18">
         <v>8</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="21">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23">
+      <c r="A12" s="18">
         <v>9</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="21">
         <v>0</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
+      <c r="A13" s="18">
         <v>10</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="21">
         <v>0</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
+      <c r="A15" s="18">
         <v>11</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="18">
         <v>2</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="20">
         <v>1</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+      <c r="A16" s="18">
         <v>12</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="18">
         <v>2</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="20">
         <v>1</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
         <v>13</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="18">
         <v>2</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="20">
         <v>1</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
         <v>14</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="18">
         <v>2</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="20">
         <v>1</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23">
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
         <v>15</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="18">
         <v>2</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="20">
         <v>1</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
         <v>16</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="18">
         <v>2</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="27">
         <v>0.5</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-    </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
         <v>17</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="18">
         <v>2</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="27">
         <v>0.5</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-    </row>
-    <row r="22" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
         <v>18</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B22" s="18">
         <v>2</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="27">
         <v>0.5</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
         <v>19</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="20">
         <v>1</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23">
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
         <v>20</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="20">
         <v>1</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23">
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
         <v>21</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="20">
         <v>1</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
         <v>22</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="24"/>
+      <c r="H26" s="26">
+        <v>46064</v>
+      </c>
+      <c r="I26" s="24"/>
+      <c r="J26" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>23</v>
+      </c>
+      <c r="B27" s="18">
+        <v>2</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="28">
         <v>0</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F27" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23">
-        <v>23</v>
-      </c>
-      <c r="B27" s="23">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
+        <v>24</v>
+      </c>
+      <c r="B28" s="18">
         <v>2</v>
       </c>
-      <c r="C27" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" s="30" t="s">
+      <c r="C28" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E28" s="28">
         <v>0</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F28" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23">
-        <v>24</v>
-      </c>
-      <c r="B28" s="23">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>25</v>
+      </c>
+      <c r="B29" s="18">
         <v>2</v>
       </c>
-      <c r="C28" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D28" s="30" t="s">
+      <c r="C29" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E29" s="28">
         <v>0</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F29" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-    </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23">
-        <v>25</v>
-      </c>
-      <c r="B29" s="23">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18">
+        <v>26</v>
+      </c>
+      <c r="B30" s="18">
         <v>2</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="30" t="s">
+      <c r="C30" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E30" s="28">
         <v>0</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F30" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-    </row>
-    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23">
-        <v>26</v>
-      </c>
-      <c r="B30" s="23">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
+        <v>27</v>
+      </c>
+      <c r="B31" s="18">
         <v>2</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="30" t="s">
+      <c r="C31" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E31" s="28">
         <v>0</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F31" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-    </row>
-    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23">
-        <v>27</v>
-      </c>
-      <c r="B31" s="23">
-        <v>2</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="34">
-        <v>0</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23">
+      <c r="A33" s="18">
         <v>28</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="18">
         <v>3</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="18"/>
     </row>
     <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23">
+      <c r="A34" s="18">
         <v>29</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="18">
         <v>3</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="18"/>
     </row>
     <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23">
+      <c r="A35" s="18">
         <v>30</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="18">
         <v>3</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="18"/>
     </row>
     <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23">
+      <c r="A36" s="18">
         <v>31</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="18">
         <v>3</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="18"/>
     </row>
     <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23">
+      <c r="A37" s="18">
         <v>32</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="18">
         <v>3</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="18"/>
     </row>
     <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23">
+      <c r="A38" s="18">
         <v>33</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="18">
         <v>3</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="18"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
     </row>
     <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23">
+      <c r="A40" s="18">
         <v>34</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B40" s="18">
         <v>4</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="18"/>
     </row>
     <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="23">
+      <c r="A41" s="18">
         <v>35</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="18">
         <v>4</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="18"/>
     </row>
     <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="23">
+      <c r="A42" s="18">
         <v>36</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B42" s="18">
         <v>4</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="18"/>
     </row>
     <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23">
+      <c r="A43" s="18">
         <v>37</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B43" s="18">
         <v>4</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="18"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
     </row>
     <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23">
+      <c r="A45" s="18">
         <v>38</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="18">
         <v>5</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="18"/>
     </row>
     <row r="46" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23">
+      <c r="A46" s="18">
         <v>39</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B46" s="18">
         <v>5</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="18"/>
     </row>
     <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+      <c r="A47" s="18">
         <v>40</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B47" s="18">
         <v>5</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="18"/>
     </row>
     <row r="48" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="23">
+      <c r="A48" s="18">
         <v>41</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B48" s="18">
         <v>5</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="18"/>
     </row>
     <row r="49" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23">
+      <c r="A49" s="18">
         <v>42</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B49" s="18">
         <v>5</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="18"/>
     </row>
     <row r="50" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="23">
+      <c r="A50" s="18">
         <v>43</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B50" s="18">
         <v>5</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="18"/>
     </row>
     <row r="51" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23">
+      <c r="A51" s="18">
         <v>44</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="18">
         <v>5</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="18"/>
     </row>
     <row r="52" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="23">
+      <c r="A52" s="18">
         <v>45</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B52" s="18">
         <v>5</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="18"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="25"/>
-      <c r="J53" s="25"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
     </row>
     <row r="54" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23">
+      <c r="A54" s="18">
         <v>46</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B54" s="18">
         <v>6</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="18"/>
     </row>
     <row r="55" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23">
+      <c r="A55" s="18">
         <v>47</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B55" s="18">
         <v>6</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="18"/>
     </row>
     <row r="56" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23">
+      <c r="A56" s="18">
         <v>48</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B56" s="18">
         <v>6</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
-      <c r="J56" s="30"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="18"/>
     </row>
     <row r="57" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="23">
+      <c r="A57" s="18">
         <v>49</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B57" s="18">
         <v>6</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="18"/>
     </row>
     <row r="58" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23">
+      <c r="A58" s="18">
         <v>50</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B58" s="18">
         <v>6</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="18"/>
     </row>
     <row r="59" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="23">
+      <c r="A59" s="18">
         <v>51</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B59" s="18">
         <v>6</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="18"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="25" t="s">
+      <c r="A60" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
-      <c r="J60" s="25"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
     </row>
     <row r="61" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="23">
+      <c r="A61" s="18">
         <v>52</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B61" s="18">
         <v>7</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="18"/>
     </row>
     <row r="62" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="23">
+      <c r="A62" s="18">
         <v>53</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B62" s="18">
         <v>7</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="30"/>
-      <c r="H62" s="30"/>
-      <c r="I62" s="30"/>
-      <c r="J62" s="30"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="18"/>
     </row>
     <row r="63" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="23">
+      <c r="A63" s="18">
         <v>54</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="18">
         <v>7</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="30"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="30"/>
-      <c r="J63" s="30"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="18"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="25" t="s">
+      <c r="A64" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-      <c r="J64" s="25"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
     </row>
     <row r="65" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="23">
+      <c r="A65" s="18">
         <v>55</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="18">
         <v>8</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="30"/>
-      <c r="J65" s="30"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="18"/>
     </row>
     <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="23">
+      <c r="A66" s="18">
         <v>56</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B66" s="18">
         <v>8</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="30"/>
-      <c r="J66" s="30"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="18"/>
     </row>
     <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23">
+      <c r="A67" s="18">
         <v>57</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B67" s="18">
         <v>8</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="18"/>
     </row>
     <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="23">
+      <c r="A68" s="18">
         <v>58</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B68" s="18">
         <v>8</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
-      <c r="J68" s="30"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="18"/>
     </row>
     <row r="69" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="23">
+      <c r="A69" s="18">
         <v>59</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="18">
         <v>8</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="30"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2824,7 +2840,7 @@
     <col min="4" max="4" width="62.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="44" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="18"/>
+    <col min="7" max="7" width="9.140625" style="13"/>
     <col min="8" max="8" width="48.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2835,1126 +2851,1126 @@
       <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="12"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="37"/>
+      <c r="E3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="12"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="9" t="s">
+      <c r="A4" s="34"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="37"/>
+      <c r="E4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="12"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="37"/>
+      <c r="E5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="12"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="34"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="12"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="34"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="37"/>
+      <c r="E7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="12"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="37"/>
+      <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="12"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="6"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="12" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="12"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="6"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="12" t="s">
+      <c r="A10" s="34"/>
+      <c r="B10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="12"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="6"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="12" t="s">
+      <c r="A11" s="34"/>
+      <c r="B11" s="36"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="12"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="6"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="12" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="12"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="6"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="16" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="15" t="s">
+      <c r="F13" s="5"/>
+      <c r="G13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="6"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="12" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="13"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="38"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="6"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="12" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="13"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="6"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="16" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="12"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="6"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="12" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="12"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="6"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12" t="s">
+      <c r="A18" s="34"/>
+      <c r="B18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="12"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="16" t="s">
+      <c r="A20" s="34"/>
+      <c r="B20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="6"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="16" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="9" t="s">
+      <c r="F21" s="4"/>
+      <c r="G21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="12"/>
+      <c r="H21" s="8"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="6"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="12" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="12"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="6"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="12" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="12"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="12" t="s">
+      <c r="D24" s="37"/>
+      <c r="E24" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="12"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="12" t="s">
+      <c r="D25" s="37"/>
+      <c r="E25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="12"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="16" t="s">
+      <c r="D26" s="37"/>
+      <c r="E26" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="15" t="s">
+      <c r="F26" s="4"/>
+      <c r="G26" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="12"/>
+      <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="12" t="s">
+      <c r="D27" s="37"/>
+      <c r="E27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="13" t="s">
+      <c r="G27" s="10"/>
+      <c r="H27" s="38" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="12" t="s">
+      <c r="D28" s="37"/>
+      <c r="E28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="13"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="38"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="14"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="16" t="s">
+      <c r="D30" s="37"/>
+      <c r="E30" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15" t="s">
+      <c r="F30" s="10"/>
+      <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="14"/>
+      <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="17" t="s">
+      <c r="D31" s="37"/>
+      <c r="E31" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="14"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="17" t="s">
+      <c r="D32" s="37"/>
+      <c r="E32" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="14"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="17" t="s">
+      <c r="D33" s="37"/>
+      <c r="E33" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="14"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" spans="4:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="37"/>
+      <c r="E34" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="14"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="14"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9"/>
     </row>
     <row r="36" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="16" t="s">
+      <c r="D36" s="37"/>
+      <c r="E36" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="12"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="8"/>
     </row>
     <row r="37" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="12" t="s">
+      <c r="D37" s="37"/>
+      <c r="E37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F37" s="7"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="12"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="8"/>
     </row>
     <row r="38" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="12" t="s">
+      <c r="D38" s="37"/>
+      <c r="E38" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="12"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="8"/>
     </row>
     <row r="39" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="37"/>
+      <c r="E39" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="12"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="8"/>
     </row>
     <row r="40" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="12" t="s">
+      <c r="D40" s="37"/>
+      <c r="E40" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="12"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="8"/>
     </row>
     <row r="41" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="12" t="s">
+      <c r="D41" s="37"/>
+      <c r="E41" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="7"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="12"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="8"/>
     </row>
     <row r="42" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="12" t="s">
+      <c r="D42" s="37"/>
+      <c r="E42" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="12"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="8"/>
     </row>
     <row r="43" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="12"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="8"/>
     </row>
     <row r="44" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="16" t="s">
+      <c r="D44" s="37"/>
+      <c r="E44" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="12"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="8"/>
     </row>
     <row r="45" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="16" t="s">
+      <c r="D45" s="37"/>
+      <c r="E45" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="12"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="8"/>
     </row>
     <row r="46" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="12" t="s">
+      <c r="D46" s="37"/>
+      <c r="E46" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="12"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="8"/>
     </row>
     <row r="47" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="12" t="s">
+      <c r="D47" s="37"/>
+      <c r="E47" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="12"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="8"/>
     </row>
     <row r="48" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="12" t="s">
+      <c r="D48" s="37"/>
+      <c r="E48" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="12"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="8"/>
     </row>
     <row r="49" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="12" t="s">
+      <c r="D49" s="37"/>
+      <c r="E49" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="12"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="8"/>
     </row>
     <row r="50" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="12" t="s">
+      <c r="D50" s="37"/>
+      <c r="E50" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="12"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="8"/>
     </row>
     <row r="51" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="12" t="s">
+      <c r="D51" s="37"/>
+      <c r="E51" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="12"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="8"/>
     </row>
     <row r="52" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="12"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="8"/>
     </row>
     <row r="53" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D53" s="10"/>
-      <c r="E53" s="16" t="s">
+      <c r="D53" s="37"/>
+      <c r="E53" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="7"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="12"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="8"/>
     </row>
     <row r="54" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D54" s="10"/>
-      <c r="E54" s="12" t="s">
+      <c r="D54" s="37"/>
+      <c r="E54" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="7"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="12"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="8"/>
     </row>
     <row r="55" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D55" s="10"/>
-      <c r="E55" s="12" t="s">
+      <c r="D55" s="37"/>
+      <c r="E55" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="7"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="12"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="8"/>
     </row>
     <row r="56" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D56" s="10"/>
-      <c r="E56" s="12" t="s">
+      <c r="D56" s="37"/>
+      <c r="E56" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="7"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="12"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="8"/>
     </row>
     <row r="57" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D57" s="10"/>
-      <c r="E57" s="12" t="s">
+      <c r="D57" s="37"/>
+      <c r="E57" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F57" s="7"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="12"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="8"/>
     </row>
     <row r="58" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D58" s="10"/>
-      <c r="E58" s="12" t="s">
+      <c r="D58" s="37"/>
+      <c r="E58" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="7"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="12"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="8"/>
     </row>
     <row r="59" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D59" s="10"/>
-      <c r="E59" s="12" t="s">
+      <c r="D59" s="37"/>
+      <c r="E59" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="12"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="8"/>
     </row>
     <row r="60" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D60" s="10"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="12"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="8"/>
     </row>
     <row r="61" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D61" s="10"/>
-      <c r="E61" s="16" t="s">
+      <c r="D61" s="37"/>
+      <c r="E61" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="7"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="12"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="8"/>
     </row>
     <row r="62" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D62" s="10"/>
-      <c r="E62" s="16" t="s">
+      <c r="D62" s="37"/>
+      <c r="E62" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="12"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="8"/>
     </row>
     <row r="63" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D63" s="10"/>
-      <c r="E63" s="12" t="s">
+      <c r="D63" s="37"/>
+      <c r="E63" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="12"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="8"/>
     </row>
     <row r="64" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D64" s="10"/>
-      <c r="E64" s="12" t="s">
+      <c r="D64" s="37"/>
+      <c r="E64" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="7"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="12"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="8"/>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D65" s="10"/>
-      <c r="E65" s="16" t="s">
+      <c r="D65" s="37"/>
+      <c r="E65" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="7"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="12"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="8"/>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D66" s="10"/>
-      <c r="E66" s="12" t="s">
+      <c r="D66" s="37"/>
+      <c r="E66" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="7"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="12"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="8"/>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D67" s="10"/>
-      <c r="E67" s="12" t="s">
+      <c r="D67" s="37"/>
+      <c r="E67" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="7"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="12"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="8"/>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D68" s="10"/>
-      <c r="E68" s="16" t="s">
+      <c r="D68" s="37"/>
+      <c r="E68" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="12"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="8"/>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D69" s="10"/>
-      <c r="E69" s="12" t="s">
+      <c r="D69" s="37"/>
+      <c r="E69" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="12"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="8"/>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D70" s="10"/>
-      <c r="E70" s="12" t="s">
+      <c r="D70" s="37"/>
+      <c r="E70" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="12"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="8"/>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D71" s="10"/>
-      <c r="E71" s="12" t="s">
+      <c r="D71" s="37"/>
+      <c r="E71" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F71" s="7"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="12"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="8"/>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="10"/>
-      <c r="E72" s="12" t="s">
+      <c r="D72" s="37"/>
+      <c r="E72" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F72" s="7"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="12"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="8"/>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D73" s="10"/>
-      <c r="E73" s="12" t="s">
+      <c r="D73" s="37"/>
+      <c r="E73" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="12"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="8"/>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D74" s="10"/>
-      <c r="E74" s="12" t="s">
+      <c r="D74" s="37"/>
+      <c r="E74" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F74" s="7"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="12"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="8"/>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D75" s="10"/>
-      <c r="E75" s="16" t="s">
+      <c r="D75" s="37"/>
+      <c r="E75" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F75" s="7"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="12"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="10"/>
+      <c r="H75" s="8"/>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="10"/>
-      <c r="E76" s="12" t="s">
+      <c r="D76" s="37"/>
+      <c r="E76" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F76" s="7"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="12"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="8"/>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="10"/>
-      <c r="E77" s="12" t="s">
+      <c r="D77" s="37"/>
+      <c r="E77" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F77" s="7"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="12"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="8"/>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D78" s="10"/>
-      <c r="E78" s="12" t="s">
+      <c r="D78" s="37"/>
+      <c r="E78" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F78" s="7"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="12"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="8"/>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D79" s="10"/>
-      <c r="E79" s="12" t="s">
+      <c r="D79" s="37"/>
+      <c r="E79" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F79" s="7"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="12"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="8"/>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D80" s="10"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="12"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="8"/>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D81" s="10"/>
-      <c r="E81" s="16" t="s">
+      <c r="D81" s="37"/>
+      <c r="E81" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F81" s="7"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="12"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="8"/>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D82" s="10"/>
-      <c r="E82" s="16" t="s">
+      <c r="D82" s="37"/>
+      <c r="E82" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F82" s="7"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="12"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="8"/>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D83" s="10"/>
-      <c r="E83" s="12" t="s">
+      <c r="D83" s="37"/>
+      <c r="E83" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F83" s="7"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="12"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="8"/>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D84" s="10"/>
-      <c r="E84" s="16" t="s">
+      <c r="D84" s="37"/>
+      <c r="E84" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F84" s="7"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="12"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="10"/>
+      <c r="H84" s="8"/>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D85" s="10"/>
-      <c r="E85" s="12" t="s">
+      <c r="D85" s="37"/>
+      <c r="E85" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F85" s="7"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="12"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="8"/>
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D86" s="10"/>
-      <c r="E86" s="12" t="s">
+      <c r="D86" s="37"/>
+      <c r="E86" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F86" s="7"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="12"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="8"/>
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D87" s="10"/>
-      <c r="E87" s="12" t="s">
+      <c r="D87" s="37"/>
+      <c r="E87" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F87" s="7"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="12"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="10"/>
+      <c r="H87" s="8"/>
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D88" s="10"/>
-      <c r="E88" s="12" t="s">
+      <c r="D88" s="37"/>
+      <c r="E88" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F88" s="7"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="12"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="8"/>
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D89" s="10"/>
-      <c r="E89" s="12" t="s">
+      <c r="D89" s="37"/>
+      <c r="E89" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F89" s="7"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="12"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="10"/>
+      <c r="H89" s="8"/>
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D90" s="10"/>
-      <c r="E90" s="12" t="s">
+      <c r="D90" s="37"/>
+      <c r="E90" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F90" s="7"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="12"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="10"/>
+      <c r="H90" s="8"/>
     </row>
     <row r="91" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D91" s="10"/>
-      <c r="E91" s="16" t="s">
+      <c r="D91" s="37"/>
+      <c r="E91" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F91" s="7"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="12"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="10"/>
+      <c r="H91" s="8"/>
     </row>
     <row r="92" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D92" s="10"/>
-      <c r="E92" s="12" t="s">
+      <c r="D92" s="37"/>
+      <c r="E92" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F92" s="7"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="12"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="8"/>
     </row>
     <row r="93" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D93" s="10"/>
-      <c r="E93" s="12" t="s">
+      <c r="D93" s="37"/>
+      <c r="E93" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F93" s="7"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="12"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="8"/>
     </row>
     <row r="94" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D94" s="10"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="12"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="8"/>
     </row>
     <row r="95" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D95" s="10"/>
-      <c r="E95" s="16" t="s">
+      <c r="D95" s="37"/>
+      <c r="E95" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F95" s="7"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="12"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="8"/>
     </row>
     <row r="96" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D96" s="10"/>
-      <c r="E96" s="12" t="s">
+      <c r="D96" s="37"/>
+      <c r="E96" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F96" s="7"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="12"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="8"/>
     </row>
     <row r="97" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D97" s="10"/>
-      <c r="E97" s="12" t="s">
+      <c r="D97" s="37"/>
+      <c r="E97" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F97" s="7"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="12"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="8"/>
     </row>
     <row r="98" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D98" s="10"/>
-      <c r="E98" s="12" t="s">
+      <c r="D98" s="37"/>
+      <c r="E98" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F98" s="7"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="12"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="8"/>
     </row>
     <row r="99" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D99" s="10"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="12"/>
+      <c r="D99" s="37"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="8"/>
     </row>
     <row r="100" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D100" s="10"/>
-      <c r="E100" s="16" t="s">
+      <c r="D100" s="37"/>
+      <c r="E100" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="F100" s="7"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="12"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="8"/>
     </row>
     <row r="101" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D101" s="10"/>
-      <c r="E101" s="16" t="s">
+      <c r="D101" s="37"/>
+      <c r="E101" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F101" s="7"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="12"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="8"/>
     </row>
     <row r="102" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D102" s="10"/>
-      <c r="E102" s="12" t="s">
+      <c r="D102" s="37"/>
+      <c r="E102" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F102" s="7"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="12"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="10"/>
+      <c r="H102" s="8"/>
     </row>
     <row r="103" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D103" s="10"/>
-      <c r="E103" s="12" t="s">
+      <c r="D103" s="37"/>
+      <c r="E103" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F103" s="7"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="12"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="10"/>
+      <c r="H103" s="8"/>
     </row>
     <row r="104" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D104" s="10"/>
-      <c r="E104" s="12" t="s">
+      <c r="D104" s="37"/>
+      <c r="E104" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F104" s="7"/>
-      <c r="G104" s="15"/>
-      <c r="H104" s="12"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="10"/>
+      <c r="H104" s="8"/>
     </row>
     <row r="105" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D105" s="10"/>
-      <c r="E105" s="12" t="s">
+      <c r="D105" s="37"/>
+      <c r="E105" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F105" s="7"/>
-      <c r="G105" s="15"/>
-      <c r="H105" s="12"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="10"/>
+      <c r="H105" s="8"/>
     </row>
     <row r="106" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D106" s="10"/>
-      <c r="E106" s="12" t="s">
+      <c r="D106" s="37"/>
+      <c r="E106" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="F106" s="7"/>
-      <c r="G106" s="15"/>
-      <c r="H106" s="12"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="10"/>
+      <c r="H106" s="8"/>
     </row>
     <row r="107" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D107" s="10"/>
+      <c r="D107" s="37"/>
     </row>
     <row r="108" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D108" s="10"/>
+      <c r="D108" s="37"/>
     </row>
     <row r="109" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D109" s="10"/>
+      <c r="D109" s="37"/>
     </row>
     <row r="110" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D110" s="10"/>
+      <c r="D110" s="37"/>
     </row>
     <row r="111" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D111" s="10"/>
+      <c r="D111" s="37"/>
     </row>
     <row r="112" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D112" s="10"/>
+      <c r="D112" s="37"/>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D113" s="10"/>
+      <c r="D113" s="37"/>
     </row>
     <row r="114" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D114" s="10"/>
+      <c r="D114" s="37"/>
     </row>
     <row r="115" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D115" s="10"/>
+      <c r="D115" s="37"/>
     </row>
     <row r="116" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D116" s="10"/>
+      <c r="D116" s="37"/>
     </row>
     <row r="117" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D117" s="10"/>
+      <c r="D117" s="37"/>
     </row>
     <row r="118" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D118" s="10"/>
+      <c r="D118" s="37"/>
     </row>
     <row r="119" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D119" s="10"/>
+      <c r="D119" s="37"/>
     </row>
     <row r="120" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D120" s="10"/>
+      <c r="D120" s="37"/>
     </row>
     <row r="121" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D121" s="10"/>
+      <c r="D121" s="37"/>
     </row>
     <row r="122" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D122" s="10"/>
+      <c r="D122" s="37"/>
     </row>
     <row r="123" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D123" s="10"/>
+      <c r="D123" s="37"/>
     </row>
     <row r="124" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D124" s="10"/>
+      <c r="D124" s="37"/>
     </row>
     <row r="125" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D125" s="10"/>
+      <c r="D125" s="37"/>
     </row>
     <row r="126" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D126" s="10"/>
+      <c r="D126" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
